--- a/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_APPLIED_STATISTICS.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_APPLIED_STATISTICS.xlsx
@@ -482,19 +482,19 @@
         <v>Trong phân phối lệch (skewed distribution), trung bình cộng (Mean) bị ảnh hưởng mạnh bởi các outliers. Trung vị (Median) giữ nguyên tính chất phân vị 50% nên phản ánh trung thực hơn.</v>
       </c>
       <c r="E3" t="str">
+        <v>Yếu vị (Mode) — chỉ phản ánh mức lương có số lượng người nhận nhiều nhất cụ thể</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Độ lệch chuẩn (Standard Deviation) — chỉ đo lường mức độ biến động chứ không phản ánh giá trị trung tâm</v>
+      </c>
+      <c r="G3" t="str">
         <v>Trung vị (Median) — không bị bóp méo bởi một số ít giá trị cực trị (outliers) quá lớn</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>Trung bình cộng (Mean) — bị kéo lệch lên cao bởi những người cực giàu</v>
       </c>
-      <c r="G3" t="str">
-        <v>Yếu vị (Mode) — chỉ phản ánh mức lương có số lượng người nhận nhiều nhất cụ thể</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Độ lệch chuẩn (Standard Deviation) — chỉ đo lường mức độ biến động chứ không phản ánh giá trị trung tâm</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>Mức độ phân tán của các điểm dữ liệu xung quanh giá trị trung bình cộng của chúng — độ biến động dữ liệu</v>
       </c>
       <c r="F4" t="str">
+        <v>Tần suất xuất hiện trung bình của các giá trị trùng lặp trong tập dữ liệu</v>
+      </c>
+      <c r="G4" t="str">
         <v>Mức độ tương quan tuyến tính giữa hai biến số độc lập với nhau</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Giá trị trung bình của khoảng cách giữa giá trị lớn nhất và nhỏ nhất</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Tần suất xuất hiện trung bình của các giá trị trùng lặp trong tập dữ liệu</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -540,19 +540,19 @@
         <v>Correlation không có nghĩa là Causation. Hai biến có thể tương quan mạnh do cùng phụ thuộc vào một biến thứ ba (confounding variable), chứ không trực tiếp gây ra nhau.</v>
       </c>
       <c r="E5" t="str">
+        <v>Tương quan chỉ áp dụng cho số liệu kinh tế; Nhân quả chỉ áp dụng cho số liệu y học</v>
+      </c>
+      <c r="F5" t="str">
         <v>Tương quan chỉ ra hai biến biến đổi cùng nhau; Nhân quả khẳng định sự thay đổi của biến này trực tiếp tạo ra sự thay đổi của biến kia</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Tương quan bắt buộc phải có giá trị âm; Nhân quả bắt buộc phải có giá trị dương</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tương quan chỉ áp dụng cho số liệu kinh tế; Nhân quả chỉ áp dụng cho số liệu y học</v>
       </c>
       <c r="H5" t="str">
         <v>Tương quan là mối quan hệ chắc chắn 100%; Nhân quả chỉ là giả thuyết thống kê</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,10 +572,10 @@
         <v>Biểu đồ đường (Line Chart) — thể hiện xu hướng liên tục và sự thay đổi theo tiến trình thời gian</v>
       </c>
       <c r="F6" t="str">
+        <v>Biểu đồ phân tán (Scatter Plot) — thể hiện mối quan hệ và sự phân bố giữa hai biến số</v>
+      </c>
+      <c r="G6" t="str">
         <v>Biểu đồ tròn (Pie Chart) — thể hiện tỷ lệ phần trăm đóng góp của các phần trong tổng thể tĩnh</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Biểu đồ phân tán (Scatter Plot) — thể hiện mối quan hệ và sự phân bố giữa hai biến số</v>
       </c>
       <c r="H6" t="str">
         <v>Biểu đồ bản đồ nhiệt (Heatmap) — thể hiện mật độ dữ liệu thông qua màu sắc tương phản</v>
@@ -598,19 +598,19 @@
         <v>Pie chart chỉ hiệu quả khi so sánh các phần của một tổng thể (phải cộng lại bằng 100%) và có ít danh mục. Có quá nhiều lát cắt sẽ khiến biểu đồ cực kỳ khó đọc.</v>
       </c>
       <c r="E7" t="str">
+        <v>Trực quan hóa sự biến động của giá cổ phiếu liên tục trong vòng 30 ngày</v>
+      </c>
+      <c r="F7" t="str">
         <v>So sánh tỷ lệ phần trăm đóng góp của một số ít danh mục (dưới 5) cấu thành nên một tổng thể 100%</v>
       </c>
-      <c r="F7" t="str">
-        <v>Trực quan hóa sự biến động của giá cổ phiếu liên tục trong vòng 30 ngày</v>
-      </c>
       <c r="G7" t="str">
+        <v>Thể hiện sự phân bố tần suất của các nhóm tuổi học sinh trong một trường học</v>
+      </c>
+      <c r="H7" t="str">
         <v>So sánh doanh thu của 50 chi nhánh cửa hàng khác nhau trên toàn quốc</v>
       </c>
-      <c r="H7" t="str">
-        <v>Thể hiện sự phân bố tần suất của các nhóm tuổi học sinh trong một trường học</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -633,10 +633,10 @@
         <v>Tỷ lệ phần trăm dữ liệu bị lỗi hoặc khuyết thiếu trong tập dữ liệu thử nghiệm</v>
       </c>
       <c r="G8" t="str">
+        <v>Mức độ chênh lệch giữa giá trị trung bình và giá trị trung vị của tập dữ liệu</v>
+      </c>
+      <c r="H8" t="str">
         <v>Độ tin cậy của mô hình dự báo tuyến tính khi số lượng quan sát tăng lên</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Mức độ chênh lệch giữa giá trị trung bình và giá trị trung vị của tập dữ liệu</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -656,19 +656,19 @@
         <v>Hướng đi lên thể hiện mối quan hệ đồng biến (tương quan dương). Độ dốc và khoảng cách các điểm đến đường thẳng xu hướng thể hiện độ mạnh yếu của tương quan.</v>
       </c>
       <c r="E9" t="str">
+        <v>Mối quan hệ tương quan âm (Negative Correlation) giữa hai biến số — biến X tăng thì biến Y giảm</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Không tồn tại bất kỳ mối liên hệ nào giữa hai biến số đang xét</v>
+      </c>
+      <c r="G9" t="str">
         <v>Mối quan hệ tương quan dương (Positive Correlation) giữa hai biến số — biến X tăng thì biến Y cũng có xu hướng tăng</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Mối quan hệ tương quan âm (Negative Correlation) giữa hai biến số — biến X tăng thì biến Y giảm</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Không tồn tại bất kỳ mối liên hệ nào giữa hai biến số đang xét</v>
       </c>
       <c r="H9" t="str">
         <v>Dữ liệu bị lỗi thu thập dẫn đến phân phối không đều</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -688,13 +688,13 @@
         <v>Bác bỏ giả thuyết không (Null Hypothesis) khi nó thực sự đúng — lỗi dương tính giả (false positive)</v>
       </c>
       <c r="F10" t="str">
+        <v>Không thể thực hiện kiểm định do kích thước mẫu khảo sát quá nhỏ dưới giới hạn</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Tính toán sai giá trị trung bình của mẫu dữ liệu khảo sát ban đầu</v>
+      </c>
+      <c r="H10" t="str">
         <v>Chấp nhận giả thuyết không khi nó thực sự sai — lỗi âm tính giả (false negative)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Không thể thực hiện kiểm định do kích thước mẫu khảo sát quá nhỏ dưới giới hạn</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Tính toán sai giá trị trung bình của mẫu dữ liệu khảo sát ban đầu</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -714,19 +714,19 @@
         <v>Cohort Analysis chia người dùng thành các nhóm (ví dụ: nhóm đăng ký vào tháng 1, tháng 2) và theo dõi tỷ lệ quay lại của từng nhóm qua các tuần/tháng tiếp theo.</v>
       </c>
       <c r="E11" t="str">
+        <v>Phân nhóm các bảng cơ sở dữ liệu quan hệ để tối ưu hóa tốc độ đọc ghi</v>
+      </c>
+      <c r="F11" t="str">
         <v>Theo dõi hành vi và mức độ giữ chân (retention) của các nhóm người dùng có chung đặc điểm khởi đầu theo thời gian — phân tích sự trung thành</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Dự báo doanh thu bán hàng của doanh nghiệp trong vòng 5 năm tới dựa trên mô hình hồi quy</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Tính toán độ lệch chuẩn của giá các loại cổ phiếu trên sàn giao dịch</v>
       </c>
-      <c r="H11" t="str">
-        <v>Phân nhóm các bảng cơ sở dữ liệu quan hệ để tối ưu hóa tốc độ đọc ghi</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>Tốc độ tăng trưởng doanh thu trung bình của một sản phẩm qua các năm tài chính</v>
       </c>
       <c r="G12" t="str">
+        <v>Số lượng biến độc lập tối đa có thể đưa vào mô hình hồi quy đa biến</v>
+      </c>
+      <c r="H12" t="str">
         <v>Xác suất mô hình dự đoán chính xác kết quả trong điều kiện thực tế</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Số lượng biến độc lập tối đa có thể đưa vào mô hình hồi quy đa biến</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -772,19 +772,19 @@
         <v>Mẫu quá nhỏ sẽ không đủ nhạy để kết luận sự khác biệt về Conversion Rate là có ý nghĩa hay chỉ là ngẫu nhiên. DA dùng công cụ tính toán Sample Size dựa trên alpha, power và MDE (Minimum Detectable Effect).</v>
       </c>
       <c r="E13" t="str">
+        <v>Để tự động tăng điểm Conversion Rate của phiên bản thử nghiệm lên tối đa</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Để đảm bảo số lượng lập trình viên viết code cho hai phiên bản là tương đương nhau</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Để giảm thiểu chi phí thuê máy chủ chạy thử nghiệm giao diện trang web</v>
+      </c>
+      <c r="H13" t="str">
         <v>Để đảm bảo thử nghiệm có đủ lực thống kê (Statistical Power) để phát hiện ra sự khác biệt thực tế giữa hai phiên bản, tránh dừng thử nghiệm quá sớm dẫn đến kết luận sai</v>
       </c>
-      <c r="F13" t="str">
-        <v>Để giảm thiểu chi phí thuê máy chủ chạy thử nghiệm giao diện trang web</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Để đảm bảo số lượng lập trình viên viết code cho hai phiên bản là tương đương nhau</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Để tự động tăng điểm Conversion Rate của phiên bản thử nghiệm lên tối đa</v>
-      </c>
       <c r="I13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>IQR = Q3 - Q1. Bất kỳ giá trị nào nằm ngoài khoảng [Q1 - 1.5*IQR, Q3 + 1.5*IQR] được coi là outlier trong phân tích Box Plot.</v>
       </c>
       <c r="E14" t="str">
+        <v>Dưới phân vị thứ 10 hoặc trên phân vị thứ 90 của toàn bộ tập dữ liệu</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Nằm ngoài khoảng từ giá trị nhỏ nhất (Min) đến giá trị lớn nhất (Max)</v>
+      </c>
+      <c r="G14" t="str">
         <v>Dưới Q1 - 1.5 * IQR hoặc trên Q3 + 1.5 * IQR — phương pháp xác định outlier bằng biểu đồ hộp (Box Plot)</v>
       </c>
-      <c r="F14" t="str">
+      <c r="H14" t="str">
         <v>Dưới giá trị trung bình trừ đi 1.5 lần độ lệch chuẩn hoặc trên giá trị trung bình cộng thêm 1.5 lần độ lệch chuẩn</v>
       </c>
-      <c r="G14" t="str">
-        <v>Nằm ngoài khoảng từ giá trị nhỏ nhất (Min) đến giá trị lớn nhất (Max)</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Dưới phân vị thứ 10 hoặc trên phân vị thứ 90 của toàn bộ tập dữ liệu</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Các kiểm định tham số giả định dữ liệu có phân phối chuẩn. Nếu dữ liệu bị lệch nặng và không thể biến đổi (transform), việc ép dùng parametric tests sẽ cho kết quả sai lệch, bắt buộc phải chuyển sang phi tham số.</v>
       </c>
       <c r="E15" t="str">
+        <v>Phân phối chuẩn chỉ áp dụng cho mẫu lớn trên 1000 phần tử; Phân phối lệch chỉ áp dụng cho mẫu nhỏ dưới 30 phần tử</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Không có ảnh hưởng nào vì mọi kiểm định thống kê đều tự động điều chỉnh phân phối dữ liệu về dạng chuẩn ở runtime</v>
+      </c>
+      <c r="G15" t="str">
         <v>Phân phối chuẩn cho phép áp dụng các kiểm định tham số (Parametric tests như t-test, ANOVA); Phân phối lệch nặng yêu cầu dùng kiểm định phi tham số (Non-parametric tests như Mann-Whitney U)</v>
       </c>
-      <c r="F15" t="str">
-        <v>Phân phối chuẩn chỉ áp dụng cho mẫu lớn trên 1000 phần tử; Phân phối lệch chỉ áp dụng cho mẫu nhỏ dưới 30 phần tử</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Phân phối chuẩn bắt buộc phải có giá trị trung bình bằng 0; Phân phối lệch có giá trị trung bình luôn dương</v>
       </c>
-      <c r="H15" t="str">
-        <v>Không có ảnh hưởng nào vì mọi kiểm định thống kê đều tự động điều chỉnh phân phối dữ liệu về dạng chuẩn ở runtime</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>CTR (Click-Through Rate) = Clicks/Impressions = 200/10,000 = 2%. CR (Conversion Rate) = Conversions/Clicks = 10/200 = 5%.</v>
       </c>
       <c r="E16" t="str">
+        <v>CTR = 5%, CR = 2% — tính ngược công thức tỷ lệ chuyển đổi và nhấp chuột</v>
+      </c>
+      <c r="F16" t="str">
         <v>CTR = 2%, CR = 5% — tính CTR dựa trên Clicks/Impressions, CR dựa trên Conversions/Clicks</v>
       </c>
-      <c r="F16" t="str">
-        <v>CTR = 5%, CR = 2% — tính ngược công thức tỷ lệ chuyển đổi và nhấp chuột</v>
-      </c>
       <c r="G16" t="str">
+        <v>CTR = 2%, CR = 0.1% — tính CR dựa trên Conversions/Impressions</v>
+      </c>
+      <c r="H16" t="str">
         <v>CTR = 0.1%, CR = 2% — tính sai hệ số chia cho tổng số hiển thị</v>
       </c>
-      <c r="H16" t="str">
-        <v>CTR = 2%, CR = 0.1% — tính CR dựa trên Conversions/Impressions</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Executive Dashboard cần sự trực quan nhanh, tập trung vào chỉ số chiến lược (High-level KPIs) và xu hướng chung. Chi tiết giao dịch thô sẽ làm loãng thông tin và gây nhiễu quyết định.</v>
       </c>
       <c r="E17" t="str">
-        <v>Chỉ hiển thị các chỉ số hiệu suất cốt lõi (KPIs) cấp cao kết hợp biểu đồ xu hướng đơn giản; hỗ trợ khả năng đi sâu (Drill-down) khi cần thiết — tránh quá tải thông tin</v>
+        <v>Đưa toàn bộ các bảng dữ liệu chi tiết thô lên màn hình chính để giám đốc kiểm tra từng giao dịch phát sinh</v>
       </c>
       <c r="F17" t="str">
-        <v>Đưa toàn bộ các bảng dữ liệu chi tiết thô lên màn hình chính để giám đốc kiểm tra từng giao dịch phát sinh</v>
+        <v>Chỉ cập nhật dữ liệu một cách thủ công mỗi năm một lần để đảm bảo tính ổn định của Dashboard</v>
       </c>
       <c r="G17" t="str">
         <v>Sử dụng tối đa các biểu đồ 3D chuyển động và hiệu ứng màu sắc tương phản mạnh để gây ấn tượng thị giác</v>
       </c>
       <c r="H17" t="str">
-        <v>Chỉ cập nhật dữ liệu một cách thủ công mỗi năm một lần để đảm bảo tính ổn định của Dashboard</v>
+        <v>Chỉ hiển thị các chỉ số hiệu suất cốt lõi (KPIs) cấp cao kết hợp biểu đồ xu hướng đơn giản; hỗ trợ khả năng đi sâu (Drill-down) khi cần thiết — tránh quá tải thông tin</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Overfitting (Quá khớp) xảy ra khi mô hình quá phức tạp, ghi nhớ cả các biến động ngẫu nhiên (noise) của tập training, dẫn đến mất đi tính tổng quát hóa (generalization) khi gặp dữ liệu thực tế mới.</v>
       </c>
       <c r="E18" t="str">
+        <v>Mô hình dự báo quá nhanh dẫn đến tràn bộ nhớ RAM của hệ thống máy chủ</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Mô hình chỉ dự báo được các giá trị âm trong khi thực tế dữ liệu luôn dương</v>
+      </c>
+      <c r="G18" t="str">
         <v>Mô hình hoạt động cực tốt trên tập dữ liệu huấn luyện (Training data) nhưng dự báo rất kém trên tập dữ liệu mới (Testing data) do học cả nhiễu của dữ liệu</v>
       </c>
-      <c r="F18" t="str">
-        <v>Mô hình dự báo quá nhanh dẫn đến tràn bộ nhớ RAM của hệ thống máy chủ</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Mô hình sử dụng quá nhiều biến độc lập dẫn đến kết quả luôn bằng 0</v>
       </c>
-      <c r="H18" t="str">
-        <v>Mô hình chỉ dự báo được các giá trị âm trong khi thực tế dữ liệu luôn dương</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Vì p-value (0.08) &gt; alpha (0.05), kết quả không đạt ý nghĩa thống kê (not statistically significant). Chúng ta thất bại trong việc bác bỏ giả thuyết Null, nghĩa là sự khác biệt chưa đủ tin cậy để khẳng định là do thay đổi thiết kế.</v>
       </c>
       <c r="E19" t="str">
+        <v>Kết luận phiên bản B chiến thắng với độ tin cậy 95% vì p-value nhỏ hơn 0.10</v>
+      </c>
+      <c r="F19" t="str">
         <v>Chưa đủ bằng chứng thống kê để bác bỏ giả thuyết không; sự gia tăng 10% này có thể do ngẫu nhiên và không nên áp dụng phiên bản B — giữ nguyên phiên bản cũ để an toàn</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Bác bỏ ngay phiên bản A và triển khai phiên bản B trên toàn hệ thống vì 10% là con số tăng trưởng rất ấn tượng thực tế</v>
       </c>
       <c r="G19" t="str">
         <v>Kéo dài thời gian thử nghiệm thêm 1 ngày rồi tự động kết luận phiên bản B chiến thắng mà không cần tính lại p-value</v>
       </c>
       <c r="H19" t="str">
-        <v>Kết luận phiên bản B chiến thắng với độ tin cậy 95% vì p-value nhỏ hơn 0.10</v>
+        <v>Bác bỏ ngay phiên bản A và triển khai phiên bản B trên toàn hệ thống vì 10% là con số tăng trưởng rất ấn tượng thực tế</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Simpson's Paradox xảy ra khi gộp dữ liệu bỏ qua trọng số hoặc tỷ lệ phân bổ của các nhóm thành phần, dẫn đến việc rút ra kết luận sai lệch nghiêm trọng nếu không phân tích phân tầng (stratified analysis).</v>
       </c>
       <c r="E20" t="str">
+        <v>Mô hình hồi quy tuyến tính dự báo kết quả hoàn toàn trái ngược với thực tế do dữ liệu bị khuyết thiếu quá nhiều</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Hai biểu đồ trực quan hóa hiển thị hai kết quả khác nhau do sử dụng hai loại thang đo khác nhau</v>
+      </c>
+      <c r="G20" t="str">
         <v>Một xu hướng xuất hiện trong các nhóm dữ liệu nhỏ biến mất hoặc đảo ngược hoàn toàn khi các nhóm được gộp chung lại với nhau — do ảnh hưởng của biến ẩn (lurking variable)</v>
       </c>
-      <c r="F20" t="str">
+      <c r="H20" t="str">
         <v>Hệ số tương quan giữa hai biến số thay đổi từ dương sang âm khi kích thước mẫu tăng lên gấp đôi</v>
       </c>
-      <c r="G20" t="str">
-        <v>Mô hình hồi quy tuyến tính dự báo kết quả hoàn toàn trái ngược với thực tế do dữ liệu bị khuyết thiếu quá nhiều</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Hai biểu đồ trực quan hóa hiển thị hai kết quả khác nhau do sử dụng hai loại thang đo khác nhau</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1007,10 +1007,10 @@
         <v>Phân tích phương sai một chiều (One-Way ANOVA) — so sánh giá trị trung bình của nhiều hơn 2 nhóm dữ liệu phân phối chuẩn</v>
       </c>
       <c r="F21" t="str">
+        <v>Kiểm định Chi-square độc lập (Chi-square test of independence) — dùng so sánh mối quan hệ giữa các biến định tính (categorical)</v>
+      </c>
+      <c r="G21" t="str">
         <v>Kiểm định T-test độc lập (Independent T-test) — chỉ giới hạn so sánh tối đa giữa 2 nhóm dữ liệu</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Kiểm định Chi-square độc lập (Chi-square test of independence) — dùng so sánh mối quan hệ giữa các biến định tính (categorical)</v>
       </c>
       <c r="H21" t="str">
         <v>Hồi quy tuyến tính đơn biến (Simple Linear Regression) — dùng để mô hình hóa mối quan hệ nhân quả</v>
@@ -1033,19 +1033,19 @@
         <v>Data-Ink Ratio = (Lượng mực dùng cho dữ liệu / Tổng lượng mực dùng cho biểu đồ). Tỷ lệ này càng cao càng tốt, nghĩa là Dashboard tối giản, tập trung truyền tải thông tin hiệu quả nhất.</v>
       </c>
       <c r="E22" t="str">
+        <v>Kích thước font chữ của các con số chỉ số quá nhỏ so với kích thước khung hình biểu đồ. Khắc phục: Tăng cỡ chữ lên gấp đôi</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Dữ liệu hiển thị bị lỗi font tiếng Việt khi xuất báo cáo sang định dạng PDF. Khắc phục: Cài đặt thêm font chữ Unicode</v>
+      </c>
+      <c r="G22" t="str">
         <v>Dashboard chứa quá nhiều chi tiết trang trí thừa, lưới dòng chằng chịt, hoặc màu nền đậm mà không chứa dữ liệu thực tế. Khắc phục: Loại bỏ tối đa các yếu tố không chứa thông tin (chartjunk) để làm nổi bật dữ liệu</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v xml:space="preserve"> Dashboard sử dụng quá ít màu mực/màu sắc dẫn đến giao diện bị đơn điệu khó nhìn. Khắc phục: Thêm nhiều hiệu ứng đổ bóng và hình nền 3D</v>
       </c>
-      <c r="G22" t="str">
-        <v>Kích thước font chữ của các con số chỉ số quá nhỏ so với kích thước khung hình biểu đồ. Khắc phục: Tăng cỡ chữ lên gấp đôi</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Dữ liệu hiển thị bị lỗi font tiếng Việt khi xuất báo cáo sang định dạng PDF. Khắc phục: Cài đặt thêm font chữ Unicode</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Đa cộng tuyến nghĩa là các biến giải thích chứa thông tin trùng lặp nhau. Nó làm cho việc ước lượng tác động riêng rẽ của từng biến lên biến phụ thuộc trở nên không chính xác (Standard errors của hệ số hồi quy bị thổi phồng).</v>
       </c>
       <c r="E23" t="str">
+        <v>Khi dữ liệu đầu vào chứa quá nhiều outliers ở các biến định lượng; làm mô hình bị overfitting</v>
+      </c>
+      <c r="F23" t="str">
         <v>Khi các biến độc lập trong mô hình có mối quan hệ tương quan mạnh với nhau; làm sai lệch hệ số hồi quy và giảm độ tin cậy của việc đánh giá tác động từng biến số</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
+        <v>Khi mô hình chạy quá lâu trên máy chủ do lượng dữ liệu đầu vào vượt quá dung lượng bộ nhớ RAM</v>
+      </c>
+      <c r="H23" t="str">
         <v>Khi biến phụ thuộc có mối quan hệ phi tuyến tính với các biến độc lập; làm giảm độ chính xác dự báo của mô hình</v>
       </c>
-      <c r="G23" t="str">
-        <v>Khi dữ liệu đầu vào chứa quá nhiều outliers ở các biến định lượng; làm mô hình bị overfitting</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Khi mô hình chạy quá lâu trên máy chủ do lượng dữ liệu đầu vào vượt quá dung lượng bộ nhớ RAM</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Mean Imputation chèn cùng một giá trị trung bình vào nhiều dòng, làm cho phân phối dữ liệu bị bó hẹp xung quanh trung bình, giảm phương sai thực tế và bóp méo mối quan hệ tương quan với các biến khác.</v>
       </c>
       <c r="E24" t="str">
+        <v>Làm thay đổi kiểu dữ liệu của cột từ kiểu số thực sang kiểu số nguyên</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Làm xuất hiện thêm nhiều giá trị trùng lặp hoàn toàn (duplications) trong cơ sở dữ liệu</v>
+      </c>
+      <c r="G24" t="str">
         <v>Làm giảm phương sai (variance) của tập dữ liệu một cách nhân tạo và làm thu hẹp khoảng tin cậy, gây sai lệch các kiểm định thống kê tiếp theo</v>
       </c>
-      <c r="F24" t="str">
+      <c r="H24" t="str">
         <v>Làm tăng kích thước file dữ liệu lên gấp đôi gây quá tải bộ nhớ lưu trữ</v>
       </c>
-      <c r="G24" t="str">
-        <v>Làm thay đổi kiểu dữ liệu của cột từ kiểu số thực sang kiểu số nguyên</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Làm xuất hiện thêm nhiều giá trị trùng lặp hoàn toàn (duplications) trong cơ sở dữ liệu</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Nếu peek liên tục và dừng khi thấy p &lt; 0.05, ta đang chọn lọc thời điểm biến động ngẫu nhiên để kết luận. Tỷ lệ dương tính giả thực tế sẽ tăng vọt từ 5% lên 20-30%. Đúng: chạy đủ Sample Size định trước rồi mới tính p-value.</v>
       </c>
       <c r="E25" t="str">
+        <v>Vì Peeking làm chậm tốc độ tải trang của hệ thống đang chạy thử nghiệm trực tiếp trên môi trường Production</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Vì Peeking bắt buộc phải sử dụng tài khoản quản trị tối cao của cơ sở dữ liệu mới thực hiện được</v>
+      </c>
+      <c r="G25" t="str">
         <v>Vì Peeking làm tăng đáng kể tỷ lệ Sai lầm loại I (Dương tính giả) do kiểm định lặp lại nhiều lần trên dữ liệu chưa đủ mẫu (Multiple Comparisons problem)</v>
       </c>
-      <c r="F25" t="str">
-        <v>Vì Peeking làm chậm tốc độ tải trang của hệ thống đang chạy thử nghiệm trực tiếp trên môi trường Production</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Vì Peeking vi phạm bản quyền thuật toán của các công cụ kiểm thử A/B thương mại chuyên nghiệp</v>
       </c>
-      <c r="H25" t="str">
-        <v>Vì Peeking bắt buộc phải sử dụng tài khoản quản trị tối cao của cơ sở dữ liệu mới thực hiện được</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1152,13 +1152,13 @@
         <v>Khi kích thước mẫu đủ lớn (n &gt;= 30), phân phối của các giá trị trung bình mẫu sẽ xấp xỉ phân phối chuẩn, bất kể phân phối của quần thể ban đầu là gì; cho phép áp dụng các kiểm định tham số (t-test)</v>
       </c>
       <c r="F26" t="str">
-        <v>Tất cả các tập dữ liệu thực tế đều tự động chuyển về phân phối chuẩn khi kích thước mẫu đạt 1000 phần tử</v>
+        <v>Độ lệch chuẩn của mẫu sẽ bằng độ lệch chuẩn của quần thể nhân với căn bậc hai của kích thước mẫu</v>
       </c>
       <c r="G26" t="str">
         <v>Giá trị trung bình của quần thể luôn bằng giá trị trung vị của mẫu khảo sát ngẫu nhiên</v>
       </c>
       <c r="H26" t="str">
-        <v>Độ lệch chuẩn của mẫu sẽ bằng độ lệch chuẩn của quần thể nhân với căn bậc hai của kích thước mẫu</v>
+        <v>Tất cả các tập dữ liệu thực tế đều tự động chuyển về phân phối chuẩn khi kích thước mẫu đạt 1000 phần tử</v>
       </c>
       <c r="I26">
         <v>1</v>
